--- a/analyst/Ines/rmonize/data_proc_elem/DPE_NAKO_INES.xlsx
+++ b/analyst/Ines/rmonize/data_proc_elem/DPE_NAKO_INES.xlsx
@@ -1,25 +1,31 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="20417"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\perrar\Documents\Perrar\NFDI4Health\TA5_1\use-cases-harmonisation\analyst\Ines\rmonize\data_proc_elem\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="K:\use-cases-harmonisation\use-cases-harmonisation\analyst\Ines\rmonize\data_proc_elem\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15290EC1-2E12-4D65-A661-7C1E9DD12E25}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="20" windowWidth="16100" windowHeight="9660"/>
+    <workbookView xWindow="-525" yWindow="1200" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="124519"/>
+  <extLst>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="315" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="323" uniqueCount="127">
   <si>
     <t>index</t>
   </si>
@@ -300,115 +306,116 @@
     <t>anthro_hueftumfang</t>
   </si>
   <si>
+    <t>operation</t>
+  </si>
+  <si>
+    <t>compatible</t>
+  </si>
+  <si>
+    <t>Sodium intake [mg/d]</t>
+  </si>
+  <si>
+    <t>Sodium to potassium intake ratio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">anthro_taillenumfang_fup
+</t>
+  </si>
+  <si>
+    <t>anthro_hueftumfang_fup</t>
+  </si>
+  <si>
+    <t>a_nu_za</t>
+  </si>
+  <si>
+    <t>a_nu_ze</t>
+  </si>
+  <si>
+    <t>a_nu_zf</t>
+  </si>
+  <si>
+    <t>a_nu_zk</t>
+  </si>
+  <si>
+    <t>a_nu_zb</t>
+  </si>
+  <si>
+    <t>a_nu_mna</t>
+  </si>
+  <si>
+    <t>a_nu_mna; a_nu_mk</t>
+  </si>
+  <si>
+    <t>a_nu_mna/a_nu_mk</t>
+  </si>
+  <si>
+    <t>a_nu_kmd</t>
+  </si>
+  <si>
+    <t>a_nu_km</t>
+  </si>
+  <si>
+    <t>a_nu_kp</t>
+  </si>
+  <si>
+    <t>Measured</t>
+  </si>
+  <si>
     <t>a_anthro_fettmasse</t>
   </si>
   <si>
-    <t>basis_age</t>
-  </si>
-  <si>
-    <t>GCAL</t>
-  </si>
-  <si>
-    <t>ZK</t>
-  </si>
-  <si>
-    <t>operation</t>
-  </si>
-  <si>
-    <t>ZK/1000</t>
-  </si>
-  <si>
-    <t>ZE</t>
-  </si>
-  <si>
-    <t>ZE/1000</t>
-  </si>
-  <si>
-    <t>ZF</t>
-  </si>
-  <si>
-    <t>ZF/1000</t>
-  </si>
-  <si>
-    <t>ZB</t>
-  </si>
-  <si>
-    <t>ZB/1000</t>
-  </si>
-  <si>
-    <t>FS</t>
-  </si>
-  <si>
-    <t>FS/1000</t>
-  </si>
-  <si>
-    <t>FU</t>
-  </si>
-  <si>
-    <t>FU/1000</t>
-  </si>
-  <si>
-    <t>FP</t>
-  </si>
-  <si>
-    <t>FP/1000</t>
-  </si>
-  <si>
-    <t>KMD</t>
-  </si>
-  <si>
-    <t>KMD/1000</t>
-  </si>
-  <si>
-    <t>KMT</t>
-  </si>
-  <si>
-    <t>KMT/1000</t>
-  </si>
-  <si>
-    <t>KMF</t>
-  </si>
-  <si>
-    <t>KMF/1000</t>
-  </si>
-  <si>
-    <t>MNA</t>
-  </si>
-  <si>
-    <t>MNA/MK</t>
-  </si>
-  <si>
-    <t>anthro_taillenumfang
-anthro_tailumfang_m</t>
-  </si>
-  <si>
-    <t>anthro_taillenumfang
-anthro_tailumfang_m</t>
-  </si>
-  <si>
-    <t>ZA</t>
-  </si>
-  <si>
-    <t>ZA/1000</t>
-  </si>
-  <si>
-    <t>compatible</t>
-  </si>
-  <si>
-    <t>MNA, MK</t>
-  </si>
-  <si>
-    <t>Sodium intake [mg/d]</t>
-  </si>
-  <si>
-    <t>Sodium to potassium intake ratio</t>
+    <t>a_nu_zk/1000</t>
+  </si>
+  <si>
+    <t>a_nu_ze/1000</t>
+  </si>
+  <si>
+    <t>a_nu_zf/1000</t>
+  </si>
+  <si>
+    <t>a_nu_za/1000</t>
+  </si>
+  <si>
+    <t>a_nu_zb/1000</t>
+  </si>
+  <si>
+    <t>a_nu_km/1000</t>
+  </si>
+  <si>
+    <t>a_nu_kp/1000</t>
+  </si>
+  <si>
+    <t>a_nu_kmd/1000</t>
+  </si>
+  <si>
+    <t>a_nu_kmt</t>
+  </si>
+  <si>
+    <t>a_nu_kmt/1000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+a_nu_kmf</t>
+  </si>
+  <si>
+    <t>a_nu_kmf/1000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">anthro_taillenumfang
+</t>
+  </si>
+  <si>
+    <t>age_anth_fup</t>
+  </si>
+  <si>
+    <t>gcal</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="5" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -420,13 +427,6 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -465,23 +465,19 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Standard" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -497,7 +493,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -572,6 +568,23 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri" panose="020F0502020204030204"/>
@@ -607,6 +620,23 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -782,17 +812,23 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:K36"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="16.08984375" customWidth="1"/>
-    <col min="3" max="3" width="35.08984375" customWidth="1"/>
-    <col min="6" max="6" width="22.1796875" customWidth="1"/>
-    <col min="8" max="8" width="10.453125" customWidth="1"/>
+    <col min="2" max="2" width="20" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="67.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="25.42578125" customWidth="1"/>
+    <col min="7" max="7" width="26.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="22.5703125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="22.42578125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="19.140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="25.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -827,7 +863,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
         <v>16</v>
       </c>
@@ -857,7 +893,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
         <v>18</v>
       </c>
@@ -887,7 +923,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
         <v>20</v>
       </c>
@@ -917,7 +953,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
         <v>22</v>
       </c>
@@ -947,7 +983,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
         <v>11</v>
       </c>
@@ -969,7 +1005,9 @@
       <c r="H6" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="I6" s="2"/>
+      <c r="I6" s="2" t="s">
+        <v>110</v>
+      </c>
       <c r="J6" s="4" t="s">
         <v>83</v>
       </c>
@@ -977,7 +1015,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
         <v>24</v>
       </c>
@@ -999,7 +1037,9 @@
       <c r="H7" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="I7" s="2"/>
+      <c r="I7" s="2" t="s">
+        <v>110</v>
+      </c>
       <c r="J7" s="4" t="s">
         <v>83</v>
       </c>
@@ -1007,7 +1047,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
         <v>26</v>
       </c>
@@ -1035,7 +1075,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
         <v>28</v>
       </c>
@@ -1063,123 +1103,135 @@
         <v>91</v>
       </c>
     </row>
-    <row r="10" spans="1:11" s="6" customFormat="1" ht="29" x14ac:dyDescent="0.35">
-      <c r="B10" s="6" t="s">
+    <row r="10" spans="1:11" s="4" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="B10" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="C10" s="6" t="s">
+      <c r="C10" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="D10" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="E10" s="6" t="s">
-        <v>80</v>
-      </c>
-      <c r="F10" s="5" t="s">
-        <v>119</v>
-      </c>
-      <c r="G10" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="H10" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="J10" s="6" t="s">
-        <v>83</v>
-      </c>
-      <c r="K10" s="6" t="s">
+      <c r="D10" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="G10" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="H10" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="I10" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="J10" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="K10" s="4" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="11" spans="1:11" s="6" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="B11" s="6" t="s">
+    <row r="11" spans="1:11" s="4" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="B11" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="C11" s="6" t="s">
+      <c r="C11" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="D11" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="E11" s="6" t="s">
-        <v>80</v>
-      </c>
-      <c r="F11" s="5" t="s">
-        <v>120</v>
-      </c>
-      <c r="G11" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="H11" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="J11" s="6" t="s">
-        <v>83</v>
-      </c>
-      <c r="K11" s="6" t="s">
+      <c r="D11" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="G11" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="H11" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="I11" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="J11" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="K11" s="4" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="12" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="B12" s="6" t="s">
+    <row r="12" spans="1:11" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B12" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="C12" s="6" t="s">
+      <c r="C12" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="D12" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="E12" s="6" t="s">
-        <v>80</v>
-      </c>
-      <c r="F12" s="6" t="s">
+      <c r="D12" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="F12" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="G12" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="H12" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="J12" s="6" t="s">
-        <v>83</v>
-      </c>
-      <c r="K12" s="6" t="s">
+      <c r="G12" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="H12" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="I12" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="J12" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="K12" s="4" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="13" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="B13" s="6" t="s">
+    <row r="13" spans="1:11" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B13" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="C13" s="6" t="s">
+      <c r="C13" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="D13" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="E13" s="6" t="s">
-        <v>80</v>
-      </c>
-      <c r="F13" s="6" t="s">
-        <v>92</v>
-      </c>
-      <c r="G13" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="H13" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="J13" s="6" t="s">
-        <v>83</v>
-      </c>
-      <c r="K13" s="6" t="s">
+      <c r="D13" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="F13" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="G13" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="H13" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="I13" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="J13" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="K13" s="4" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
         <v>38</v>
       </c>
@@ -1207,7 +1259,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
         <v>40</v>
       </c>
@@ -1235,33 +1287,34 @@
         <v>91</v>
       </c>
     </row>
-    <row r="16" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="B16" s="6" t="s">
+    <row r="16" spans="1:11" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B16" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="C16" s="6" t="s">
+      <c r="C16" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="D16" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="E16" s="6" t="s">
-        <v>80</v>
-      </c>
-      <c r="G16" s="6" t="s">
-        <v>90</v>
-      </c>
-      <c r="H16" s="6" t="s">
-        <v>90</v>
-      </c>
-      <c r="J16" s="6" t="s">
-        <v>90</v>
-      </c>
-      <c r="K16" s="6" t="s">
+      <c r="D16" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E16" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="F16" s="2"/>
+      <c r="G16" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="J16" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="K16" s="2" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="17" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B17" t="s">
         <v>44</v>
       </c>
@@ -1275,7 +1328,7 @@
         <v>80</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>93</v>
+        <v>111</v>
       </c>
       <c r="G17" s="4" t="s">
         <v>82</v>
@@ -1283,7 +1336,9 @@
       <c r="H17" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="I17" s="2"/>
+      <c r="I17" s="2" t="s">
+        <v>110</v>
+      </c>
       <c r="J17" s="4" t="s">
         <v>83</v>
       </c>
@@ -1291,21 +1346,21 @@
         <v>84</v>
       </c>
     </row>
-    <row r="18" spans="2:11" x14ac:dyDescent="0.35">
-      <c r="B18" t="s">
+    <row r="18" spans="2:11" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B18" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="C18" t="s">
+      <c r="C18" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="D18" t="s">
-        <v>13</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="F18" s="3" t="s">
-        <v>94</v>
+      <c r="D18" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E18" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="F18" s="4" t="s">
+        <v>125</v>
       </c>
       <c r="G18" s="4" t="s">
         <v>82</v>
@@ -1313,7 +1368,6 @@
       <c r="H18" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="I18" s="2"/>
       <c r="J18" s="4" t="s">
         <v>83</v>
       </c>
@@ -1321,7 +1375,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="19" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B19" t="s">
         <v>14</v>
       </c>
@@ -1335,7 +1389,7 @@
         <v>80</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>95</v>
+        <v>126</v>
       </c>
       <c r="G19" s="4" t="s">
         <v>82</v>
@@ -1351,7 +1405,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="20" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="20" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B20" t="s">
         <v>48</v>
       </c>
@@ -1365,23 +1419,23 @@
         <v>80</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="G20" s="2" t="s">
-        <v>97</v>
+        <v>102</v>
+      </c>
+      <c r="G20" s="4" t="s">
+        <v>93</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="I20" s="2"/>
       <c r="J20" s="4" t="s">
         <v>83</v>
       </c>
       <c r="K20" s="4" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="21" spans="2:11" x14ac:dyDescent="0.35">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="21" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B21" t="s">
         <v>50</v>
       </c>
@@ -1395,23 +1449,23 @@
         <v>80</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="G21" s="2" t="s">
-        <v>97</v>
+        <v>100</v>
+      </c>
+      <c r="G21" s="4" t="s">
+        <v>93</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>100</v>
+        <v>113</v>
       </c>
       <c r="I21" s="2"/>
       <c r="J21" s="4" t="s">
         <v>83</v>
       </c>
       <c r="K21" s="4" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="22" spans="2:11" x14ac:dyDescent="0.35">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="22" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B22" t="s">
         <v>52</v>
       </c>
@@ -1427,21 +1481,21 @@
       <c r="F22" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="G22" s="2" t="s">
-        <v>97</v>
+      <c r="G22" s="4" t="s">
+        <v>93</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="I22" s="2"/>
       <c r="J22" s="4" t="s">
         <v>83</v>
       </c>
       <c r="K22" s="4" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="23" spans="2:11" x14ac:dyDescent="0.35">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="23" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B23" t="s">
         <v>54</v>
       </c>
@@ -1455,22 +1509,23 @@
         <v>80</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="G23" s="2" t="s">
-        <v>97</v>
+        <v>99</v>
+      </c>
+      <c r="G23" s="4" t="s">
+        <v>93</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>122</v>
-      </c>
+        <v>115</v>
+      </c>
+      <c r="I23" s="2"/>
       <c r="J23" s="4" t="s">
         <v>83</v>
       </c>
       <c r="K23" s="4" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="24" spans="2:11" x14ac:dyDescent="0.35">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="24" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B24" t="s">
         <v>56</v>
       </c>
@@ -1486,21 +1541,21 @@
       <c r="F24" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="G24" s="2" t="s">
-        <v>97</v>
+      <c r="G24" s="4" t="s">
+        <v>93</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>104</v>
+        <v>116</v>
       </c>
       <c r="I24" s="2"/>
       <c r="J24" s="4" t="s">
         <v>83</v>
       </c>
       <c r="K24" s="4" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="25" spans="2:11" x14ac:dyDescent="0.35">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="25" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B25" t="s">
         <v>58</v>
       </c>
@@ -1513,24 +1568,22 @@
       <c r="E25" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="F25" s="3" t="s">
-        <v>105</v>
-      </c>
+      <c r="F25" s="3"/>
       <c r="G25" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="H25" s="3" t="s">
-        <v>106</v>
+        <v>90</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>90</v>
       </c>
       <c r="I25" s="2"/>
-      <c r="J25" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="K25" s="4" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="26" spans="2:11" x14ac:dyDescent="0.35">
+      <c r="J25" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="K25" s="2" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="26" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B26" t="s">
         <v>60</v>
       </c>
@@ -1544,23 +1597,23 @@
         <v>80</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="G26" s="2" t="s">
-        <v>97</v>
+        <v>108</v>
+      </c>
+      <c r="G26" s="4" t="s">
+        <v>93</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="I26" s="2"/>
       <c r="J26" s="4" t="s">
         <v>83</v>
       </c>
       <c r="K26" s="4" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="27" spans="2:11" x14ac:dyDescent="0.35">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="27" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B27" t="s">
         <v>62</v>
       </c>
@@ -1576,21 +1629,21 @@
       <c r="F27" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="G27" s="2" t="s">
-        <v>97</v>
+      <c r="G27" s="4" t="s">
+        <v>93</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>110</v>
+        <v>118</v>
       </c>
       <c r="I27" s="2"/>
       <c r="J27" s="4" t="s">
         <v>83</v>
       </c>
       <c r="K27" s="4" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="28" spans="2:11" x14ac:dyDescent="0.35">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="28" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B28" t="s">
         <v>64</v>
       </c>
@@ -1604,23 +1657,23 @@
         <v>80</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="G28" s="2" t="s">
-        <v>97</v>
+        <v>107</v>
+      </c>
+      <c r="G28" s="4" t="s">
+        <v>93</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="I28" s="2"/>
       <c r="J28" s="4" t="s">
         <v>83</v>
       </c>
       <c r="K28" s="4" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="29" spans="2:11" x14ac:dyDescent="0.35">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="29" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B29" t="s">
         <v>66</v>
       </c>
@@ -1648,7 +1701,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="30" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="30" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B30" t="s">
         <v>68</v>
       </c>
@@ -1676,7 +1729,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="31" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="31" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B31" t="s">
         <v>70</v>
       </c>
@@ -1689,24 +1742,24 @@
       <c r="E31" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="F31" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="G31" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="H31" s="2" t="s">
-        <v>114</v>
+      <c r="F31" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="G31" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="H31" s="4" t="s">
+        <v>121</v>
       </c>
       <c r="I31" s="2"/>
-      <c r="J31" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="K31" s="2" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="32" spans="2:11" x14ac:dyDescent="0.35">
+      <c r="J31" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="K31" s="4" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="32" spans="2:11" ht="30" x14ac:dyDescent="0.25">
       <c r="B32" t="s">
         <v>72</v>
       </c>
@@ -1719,24 +1772,24 @@
       <c r="E32" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="F32" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="G32" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="H32" s="2" t="s">
-        <v>116</v>
+      <c r="F32" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="G32" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="H32" s="4" t="s">
+        <v>123</v>
       </c>
       <c r="I32" s="2"/>
-      <c r="J32" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="K32" s="2" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="33" spans="2:11" x14ac:dyDescent="0.35">
+      <c r="J32" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="K32" s="4" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="33" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B33" t="s">
         <v>74</v>
       </c>
@@ -1753,7 +1806,9 @@
       <c r="G33" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="H33" s="2"/>
+      <c r="H33" s="2" t="s">
+        <v>90</v>
+      </c>
       <c r="I33" s="2"/>
       <c r="J33" s="2" t="s">
         <v>90</v>
@@ -1762,7 +1817,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="34" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="34" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B34" t="s">
         <v>76</v>
       </c>
@@ -1779,7 +1834,9 @@
       <c r="G34" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="H34" s="2"/>
+      <c r="H34" s="2" t="s">
+        <v>90</v>
+      </c>
       <c r="I34" s="2"/>
       <c r="J34" s="2" t="s">
         <v>90</v>
@@ -1788,12 +1845,12 @@
         <v>91</v>
       </c>
     </row>
-    <row r="35" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="35" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B35" t="s">
         <v>78</v>
       </c>
       <c r="C35" t="s">
-        <v>125</v>
+        <v>95</v>
       </c>
       <c r="D35" t="s">
         <v>13</v>
@@ -1802,7 +1859,7 @@
         <v>80</v>
       </c>
       <c r="F35" s="4" t="s">
-        <v>117</v>
+        <v>104</v>
       </c>
       <c r="G35" s="4" t="s">
         <v>82</v>
@@ -1818,12 +1875,12 @@
         <v>84</v>
       </c>
     </row>
-    <row r="36" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="36" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B36" t="s">
         <v>79</v>
       </c>
       <c r="C36" t="s">
-        <v>126</v>
+        <v>96</v>
       </c>
       <c r="D36" t="s">
         <v>13</v>
@@ -1832,20 +1889,20 @@
         <v>80</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>124</v>
+        <v>105</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>118</v>
+        <v>106</v>
       </c>
       <c r="I36" s="2"/>
       <c r="J36" s="2" t="s">
         <v>83</v>
       </c>
       <c r="K36" s="2" t="s">
-        <v>123</v>
+        <v>94</v>
       </c>
     </row>
   </sheetData>

--- a/analyst/Ines/rmonize/data_proc_elem/DPE_NAKO_INES.xlsx
+++ b/analyst/Ines/rmonize/data_proc_elem/DPE_NAKO_INES.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="K:\use-cases-harmonisation\use-cases-harmonisation\analyst\Ines\rmonize\data_proc_elem\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15290EC1-2E12-4D65-A661-7C1E9DD12E25}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB98EF93-84A2-46EF-936A-5615FE41ABEF}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-525" yWindow="1200" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -318,10 +318,6 @@
     <t>Sodium to potassium intake ratio</t>
   </si>
   <si>
-    <t xml:space="preserve">anthro_taillenumfang_fup
-</t>
-  </si>
-  <si>
     <t>anthro_hueftumfang_fup</t>
   </si>
   <si>
@@ -394,21 +390,22 @@
     <t>a_nu_kmt/1000</t>
   </si>
   <si>
-    <t xml:space="preserve">
-a_nu_kmf</t>
-  </si>
-  <si>
     <t>a_nu_kmf/1000</t>
   </si>
   <si>
-    <t xml:space="preserve">anthro_taillenumfang
-</t>
-  </si>
-  <si>
     <t>age_anth_fup</t>
   </si>
   <si>
     <t>gcal</t>
+  </si>
+  <si>
+    <t>anthro_taillenumfang</t>
+  </si>
+  <si>
+    <t>a_nu_kmf</t>
+  </si>
+  <si>
+    <t>anthro_taillenumfang_fup</t>
   </si>
 </sst>
 </file>
@@ -813,6 +810,9 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr>
+    <pageSetUpPr autoPageBreaks="0"/>
+  </sheetPr>
   <dimension ref="A1:K36"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1006,7 +1006,7 @@
         <v>82</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="J6" s="4" t="s">
         <v>83</v>
@@ -1038,7 +1038,7 @@
         <v>82</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="J7" s="4" t="s">
         <v>83</v>
@@ -1103,7 +1103,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="10" spans="1:11" s="4" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B10" s="4" t="s">
         <v>30</v>
       </c>
@@ -1117,7 +1117,7 @@
         <v>80</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>97</v>
+        <v>126</v>
       </c>
       <c r="G10" s="4" t="s">
         <v>82</v>
@@ -1126,7 +1126,7 @@
         <v>82</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="J10" s="4" t="s">
         <v>83</v>
@@ -1135,7 +1135,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="11" spans="1:11" s="4" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B11" s="4" t="s">
         <v>32</v>
       </c>
@@ -1158,7 +1158,7 @@
         <v>82</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="J11" s="4" t="s">
         <v>83</v>
@@ -1190,7 +1190,7 @@
         <v>82</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="J12" s="4" t="s">
         <v>83</v>
@@ -1213,7 +1213,7 @@
         <v>80</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="G13" s="4" t="s">
         <v>82</v>
@@ -1222,7 +1222,7 @@
         <v>82</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="J13" s="4" t="s">
         <v>83</v>
@@ -1328,7 +1328,7 @@
         <v>80</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="G17" s="4" t="s">
         <v>82</v>
@@ -1337,7 +1337,7 @@
         <v>82</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="J17" s="4" t="s">
         <v>83</v>
@@ -1360,7 +1360,7 @@
         <v>80</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="G18" s="4" t="s">
         <v>82</v>
@@ -1389,7 +1389,7 @@
         <v>80</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="G19" s="4" t="s">
         <v>82</v>
@@ -1419,13 +1419,13 @@
         <v>80</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="G20" s="4" t="s">
         <v>93</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="I20" s="2"/>
       <c r="J20" s="4" t="s">
@@ -1449,13 +1449,13 @@
         <v>80</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="G21" s="4" t="s">
         <v>93</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="I21" s="2"/>
       <c r="J21" s="4" t="s">
@@ -1479,13 +1479,13 @@
         <v>80</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="G22" s="4" t="s">
         <v>93</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="I22" s="2"/>
       <c r="J22" s="4" t="s">
@@ -1509,13 +1509,13 @@
         <v>80</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G23" s="4" t="s">
         <v>93</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="I23" s="2"/>
       <c r="J23" s="4" t="s">
@@ -1539,13 +1539,13 @@
         <v>80</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="G24" s="4" t="s">
         <v>93</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="I24" s="2"/>
       <c r="J24" s="4" t="s">
@@ -1597,13 +1597,13 @@
         <v>80</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="G26" s="4" t="s">
         <v>93</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="I26" s="2"/>
       <c r="J26" s="4" t="s">
@@ -1627,13 +1627,13 @@
         <v>80</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="G27" s="4" t="s">
         <v>93</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="I27" s="2"/>
       <c r="J27" s="4" t="s">
@@ -1657,13 +1657,13 @@
         <v>80</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="G28" s="4" t="s">
         <v>93</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="I28" s="2"/>
       <c r="J28" s="4" t="s">
@@ -1743,13 +1743,13 @@
         <v>80</v>
       </c>
       <c r="F31" s="4" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="G31" s="4" t="s">
         <v>93</v>
       </c>
       <c r="H31" s="4" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="I31" s="2"/>
       <c r="J31" s="4" t="s">
@@ -1759,7 +1759,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="32" spans="2:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B32" t="s">
         <v>72</v>
       </c>
@@ -1773,13 +1773,13 @@
         <v>80</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="G32" s="4" t="s">
         <v>93</v>
       </c>
       <c r="H32" s="4" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="I32" s="2"/>
       <c r="J32" s="4" t="s">
@@ -1859,7 +1859,7 @@
         <v>80</v>
       </c>
       <c r="F35" s="4" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="G35" s="4" t="s">
         <v>82</v>
@@ -1889,13 +1889,13 @@
         <v>80</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="G36" s="2" t="s">
         <v>93</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="I36" s="2"/>
       <c r="J36" s="2" t="s">

--- a/analyst/Ines/rmonize/data_proc_elem/DPE_NAKO_INES.xlsx
+++ b/analyst/Ines/rmonize/data_proc_elem/DPE_NAKO_INES.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="20417"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27932"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="K:\use-cases-harmonisation\use-cases-harmonisation\analyst\Ines\rmonize\data_proc_elem\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\schwarz-f\Desktop\use-cases-harmonisation\analyst\Ines\rmonize\data_proc_elem\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB98EF93-84A2-46EF-936A-5615FE41ABEF}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D6ACFF6-35CD-4AFB-8799-CF8622242508}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-525" yWindow="1200" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -339,9 +339,6 @@
     <t>a_nu_mna</t>
   </si>
   <si>
-    <t>a_nu_mna; a_nu_mk</t>
-  </si>
-  <si>
     <t>a_nu_mna/a_nu_mk</t>
   </si>
   <si>
@@ -406,6 +403,9 @@
   </si>
   <si>
     <t>anthro_taillenumfang_fup</t>
+  </si>
+  <si>
+    <t>a_nu_mna;a_nu_mk</t>
   </si>
 </sst>
 </file>
@@ -474,7 +474,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -490,9 +490,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -530,9 +530,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -565,26 +565,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -617,26 +600,9 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -814,7 +780,7 @@
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
   <dimension ref="A1:K36"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="20" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="67.5703125" bestFit="1" customWidth="1"/>
@@ -1006,7 +972,7 @@
         <v>82</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="J6" s="4" t="s">
         <v>83</v>
@@ -1038,7 +1004,7 @@
         <v>82</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="J7" s="4" t="s">
         <v>83</v>
@@ -1117,7 +1083,7 @@
         <v>80</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G10" s="4" t="s">
         <v>82</v>
@@ -1126,7 +1092,7 @@
         <v>82</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="J10" s="4" t="s">
         <v>83</v>
@@ -1149,7 +1115,7 @@
         <v>80</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="G11" s="4" t="s">
         <v>82</v>
@@ -1158,7 +1124,7 @@
         <v>82</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="J11" s="4" t="s">
         <v>83</v>
@@ -1190,7 +1156,7 @@
         <v>82</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="J12" s="4" t="s">
         <v>83</v>
@@ -1222,7 +1188,7 @@
         <v>82</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="J13" s="4" t="s">
         <v>83</v>
@@ -1328,7 +1294,7 @@
         <v>80</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="G17" s="4" t="s">
         <v>82</v>
@@ -1337,7 +1303,7 @@
         <v>82</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="J17" s="4" t="s">
         <v>83</v>
@@ -1360,7 +1326,7 @@
         <v>80</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="G18" s="4" t="s">
         <v>82</v>
@@ -1389,7 +1355,7 @@
         <v>80</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="G19" s="4" t="s">
         <v>82</v>
@@ -1425,7 +1391,7 @@
         <v>93</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="I20" s="2"/>
       <c r="J20" s="4" t="s">
@@ -1455,7 +1421,7 @@
         <v>93</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="I21" s="2"/>
       <c r="J21" s="4" t="s">
@@ -1485,7 +1451,7 @@
         <v>93</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="I22" s="2"/>
       <c r="J22" s="4" t="s">
@@ -1515,7 +1481,7 @@
         <v>93</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="I23" s="2"/>
       <c r="J23" s="4" t="s">
@@ -1545,7 +1511,7 @@
         <v>93</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="I24" s="2"/>
       <c r="J24" s="4" t="s">
@@ -1597,13 +1563,13 @@
         <v>80</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="G26" s="4" t="s">
         <v>93</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="I26" s="2"/>
       <c r="J26" s="4" t="s">
@@ -1627,13 +1593,13 @@
         <v>80</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="G27" s="4" t="s">
         <v>93</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="I27" s="2"/>
       <c r="J27" s="4" t="s">
@@ -1657,13 +1623,13 @@
         <v>80</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="G28" s="4" t="s">
         <v>93</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="I28" s="2"/>
       <c r="J28" s="4" t="s">
@@ -1743,13 +1709,13 @@
         <v>80</v>
       </c>
       <c r="F31" s="4" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="G31" s="4" t="s">
         <v>93</v>
       </c>
       <c r="H31" s="4" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="I31" s="2"/>
       <c r="J31" s="4" t="s">
@@ -1773,13 +1739,13 @@
         <v>80</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G32" s="4" t="s">
         <v>93</v>
       </c>
       <c r="H32" s="4" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="I32" s="2"/>
       <c r="J32" s="4" t="s">
@@ -1889,13 +1855,13 @@
         <v>80</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>104</v>
+        <v>126</v>
       </c>
       <c r="G36" s="2" t="s">
         <v>93</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="I36" s="2"/>
       <c r="J36" s="2" t="s">

--- a/analyst/Ines/rmonize/data_proc_elem/DPE_NAKO_INES.xlsx
+++ b/analyst/Ines/rmonize/data_proc_elem/DPE_NAKO_INES.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\schwarz-f\Desktop\use-cases-harmonisation\analyst\Ines\rmonize\data_proc_elem\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D6ACFF6-35CD-4AFB-8799-CF8622242508}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91AE8E90-6E77-4D94-ADAF-0308982B02BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -390,9 +390,6 @@
     <t>a_nu_kmf/1000</t>
   </si>
   <si>
-    <t>age_anth_fup</t>
-  </si>
-  <si>
     <t>gcal</t>
   </si>
   <si>
@@ -406,6 +403,9 @@
   </si>
   <si>
     <t>a_nu_mna;a_nu_mk</t>
+  </si>
+  <si>
+    <t>basis_age_fup</t>
   </si>
 </sst>
 </file>
@@ -1083,7 +1083,7 @@
         <v>80</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G10" s="4" t="s">
         <v>82</v>
@@ -1115,7 +1115,7 @@
         <v>80</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="G11" s="4" t="s">
         <v>82</v>
@@ -1326,7 +1326,7 @@
         <v>80</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="G18" s="4" t="s">
         <v>82</v>
@@ -1355,7 +1355,7 @@
         <v>80</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="G19" s="4" t="s">
         <v>82</v>
@@ -1739,7 +1739,7 @@
         <v>80</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="G32" s="4" t="s">
         <v>93</v>
@@ -1855,7 +1855,7 @@
         <v>80</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G36" s="2" t="s">
         <v>93</v>

--- a/analyst/Ines/rmonize/data_proc_elem/DPE_NAKO_INES.xlsx
+++ b/analyst/Ines/rmonize/data_proc_elem/DPE_NAKO_INES.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\schwarz-f\Desktop\use-cases-harmonisation\analyst\Ines\rmonize\data_proc_elem\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91AE8E90-6E77-4D94-ADAF-0308982B02BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D40975B1-5947-4E7A-B7CF-12E301E36BFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -294,9 +294,6 @@
     <t>a_anthro_bmi</t>
   </si>
   <si>
-    <t>anthro_bmi</t>
-  </si>
-  <si>
     <t>impossible</t>
   </si>
   <si>
@@ -390,9 +387,6 @@
     <t>a_nu_kmf/1000</t>
   </si>
   <si>
-    <t>gcal</t>
-  </si>
-  <si>
     <t>anthro_taillenumfang</t>
   </si>
   <si>
@@ -406,6 +400,12 @@
   </si>
   <si>
     <t>basis_age_fup</t>
+  </si>
+  <si>
+    <t>anthro_BMI</t>
+  </si>
+  <si>
+    <t>a_nu_gcal</t>
   </si>
 </sst>
 </file>
@@ -972,7 +972,7 @@
         <v>82</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="J6" s="4" t="s">
         <v>83</v>
@@ -995,7 +995,7 @@
         <v>80</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>89</v>
+        <v>125</v>
       </c>
       <c r="G7" s="4" t="s">
         <v>82</v>
@@ -1004,7 +1004,7 @@
         <v>82</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="J7" s="4" t="s">
         <v>83</v>
@@ -1028,17 +1028,17 @@
       </c>
       <c r="F8" s="2"/>
       <c r="G8" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="I8" s="2"/>
       <c r="J8" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="K8" s="2" t="s">
         <v>90</v>
-      </c>
-      <c r="K8" s="2" t="s">
-        <v>91</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
@@ -1056,17 +1056,17 @@
       </c>
       <c r="F9" s="2"/>
       <c r="G9" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="I9" s="2"/>
       <c r="J9" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="K9" s="2" t="s">
         <v>90</v>
-      </c>
-      <c r="K9" s="2" t="s">
-        <v>91</v>
       </c>
     </row>
     <row r="10" spans="1:11" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -1083,7 +1083,7 @@
         <v>80</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="G10" s="4" t="s">
         <v>82</v>
@@ -1092,7 +1092,7 @@
         <v>82</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="J10" s="4" t="s">
         <v>83</v>
@@ -1115,7 +1115,7 @@
         <v>80</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="G11" s="4" t="s">
         <v>82</v>
@@ -1124,7 +1124,7 @@
         <v>82</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="J11" s="4" t="s">
         <v>83</v>
@@ -1147,7 +1147,7 @@
         <v>80</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="G12" s="4" t="s">
         <v>82</v>
@@ -1156,7 +1156,7 @@
         <v>82</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="J12" s="4" t="s">
         <v>83</v>
@@ -1179,7 +1179,7 @@
         <v>80</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="G13" s="4" t="s">
         <v>82</v>
@@ -1188,7 +1188,7 @@
         <v>82</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="J13" s="4" t="s">
         <v>83</v>
@@ -1212,17 +1212,17 @@
       </c>
       <c r="F14" s="2"/>
       <c r="G14" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="I14" s="2"/>
       <c r="J14" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="K14" s="2" t="s">
         <v>90</v>
-      </c>
-      <c r="K14" s="2" t="s">
-        <v>91</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.25">
@@ -1240,17 +1240,17 @@
       </c>
       <c r="F15" s="2"/>
       <c r="G15" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="I15" s="2"/>
       <c r="J15" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="K15" s="2" t="s">
         <v>90</v>
-      </c>
-      <c r="K15" s="2" t="s">
-        <v>91</v>
       </c>
     </row>
     <row r="16" spans="1:11" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -1268,16 +1268,16 @@
       </c>
       <c r="F16" s="2"/>
       <c r="G16" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="J16" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="K16" s="2" t="s">
         <v>90</v>
-      </c>
-      <c r="H16" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="J16" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="K16" s="2" t="s">
-        <v>91</v>
       </c>
     </row>
     <row r="17" spans="2:11" x14ac:dyDescent="0.25">
@@ -1294,7 +1294,7 @@
         <v>80</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="G17" s="4" t="s">
         <v>82</v>
@@ -1303,7 +1303,7 @@
         <v>82</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="J17" s="4" t="s">
         <v>83</v>
@@ -1326,7 +1326,7 @@
         <v>80</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="G18" s="4" t="s">
         <v>82</v>
@@ -1355,7 +1355,7 @@
         <v>80</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="G19" s="4" t="s">
         <v>82</v>
@@ -1385,20 +1385,20 @@
         <v>80</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="G20" s="4" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="I20" s="2"/>
       <c r="J20" s="4" t="s">
         <v>83</v>
       </c>
       <c r="K20" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="21" spans="2:11" x14ac:dyDescent="0.25">
@@ -1415,20 +1415,20 @@
         <v>80</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G21" s="4" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="I21" s="2"/>
       <c r="J21" s="4" t="s">
         <v>83</v>
       </c>
       <c r="K21" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="22" spans="2:11" x14ac:dyDescent="0.25">
@@ -1445,20 +1445,20 @@
         <v>80</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="G22" s="4" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="I22" s="2"/>
       <c r="J22" s="4" t="s">
         <v>83</v>
       </c>
       <c r="K22" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="23" spans="2:11" x14ac:dyDescent="0.25">
@@ -1475,20 +1475,20 @@
         <v>80</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="G23" s="4" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="I23" s="2"/>
       <c r="J23" s="4" t="s">
         <v>83</v>
       </c>
       <c r="K23" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="24" spans="2:11" x14ac:dyDescent="0.25">
@@ -1505,20 +1505,20 @@
         <v>80</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="G24" s="4" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="I24" s="2"/>
       <c r="J24" s="4" t="s">
         <v>83</v>
       </c>
       <c r="K24" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="25" spans="2:11" x14ac:dyDescent="0.25">
@@ -1536,17 +1536,17 @@
       </c>
       <c r="F25" s="3"/>
       <c r="G25" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="I25" s="2"/>
       <c r="J25" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="K25" s="2" t="s">
         <v>90</v>
-      </c>
-      <c r="K25" s="2" t="s">
-        <v>91</v>
       </c>
     </row>
     <row r="26" spans="2:11" x14ac:dyDescent="0.25">
@@ -1563,20 +1563,20 @@
         <v>80</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="G26" s="4" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="I26" s="2"/>
       <c r="J26" s="4" t="s">
         <v>83</v>
       </c>
       <c r="K26" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="27" spans="2:11" x14ac:dyDescent="0.25">
@@ -1593,20 +1593,20 @@
         <v>80</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="G27" s="4" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="I27" s="2"/>
       <c r="J27" s="4" t="s">
         <v>83</v>
       </c>
       <c r="K27" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="28" spans="2:11" x14ac:dyDescent="0.25">
@@ -1623,20 +1623,20 @@
         <v>80</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="G28" s="4" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="I28" s="2"/>
       <c r="J28" s="4" t="s">
         <v>83</v>
       </c>
       <c r="K28" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="29" spans="2:11" x14ac:dyDescent="0.25">
@@ -1654,17 +1654,17 @@
       </c>
       <c r="F29" s="3"/>
       <c r="G29" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="I29" s="2"/>
       <c r="J29" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="K29" s="2" t="s">
         <v>90</v>
-      </c>
-      <c r="K29" s="2" t="s">
-        <v>91</v>
       </c>
     </row>
     <row r="30" spans="2:11" x14ac:dyDescent="0.25">
@@ -1682,17 +1682,17 @@
       </c>
       <c r="F30" s="3"/>
       <c r="G30" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="I30" s="2"/>
       <c r="J30" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="K30" s="2" t="s">
         <v>90</v>
-      </c>
-      <c r="K30" s="2" t="s">
-        <v>91</v>
       </c>
     </row>
     <row r="31" spans="2:11" x14ac:dyDescent="0.25">
@@ -1709,20 +1709,20 @@
         <v>80</v>
       </c>
       <c r="F31" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="G31" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="H31" s="4" t="s">
         <v>118</v>
-      </c>
-      <c r="G31" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="H31" s="4" t="s">
-        <v>119</v>
       </c>
       <c r="I31" s="2"/>
       <c r="J31" s="4" t="s">
         <v>83</v>
       </c>
       <c r="K31" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="32" spans="2:11" x14ac:dyDescent="0.25">
@@ -1739,20 +1739,20 @@
         <v>80</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="G32" s="4" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H32" s="4" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="I32" s="2"/>
       <c r="J32" s="4" t="s">
         <v>83</v>
       </c>
       <c r="K32" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="33" spans="2:11" x14ac:dyDescent="0.25">
@@ -1770,17 +1770,17 @@
       </c>
       <c r="F33" s="4"/>
       <c r="G33" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="I33" s="2"/>
       <c r="J33" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="K33" s="2" t="s">
         <v>90</v>
-      </c>
-      <c r="K33" s="2" t="s">
-        <v>91</v>
       </c>
     </row>
     <row r="34" spans="2:11" x14ac:dyDescent="0.25">
@@ -1798,17 +1798,17 @@
       </c>
       <c r="F34" s="4"/>
       <c r="G34" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="I34" s="2"/>
       <c r="J34" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="K34" s="2" t="s">
         <v>90</v>
-      </c>
-      <c r="K34" s="2" t="s">
-        <v>91</v>
       </c>
     </row>
     <row r="35" spans="2:11" x14ac:dyDescent="0.25">
@@ -1816,7 +1816,7 @@
         <v>78</v>
       </c>
       <c r="C35" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D35" t="s">
         <v>13</v>
@@ -1825,7 +1825,7 @@
         <v>80</v>
       </c>
       <c r="F35" s="4" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="G35" s="4" t="s">
         <v>82</v>
@@ -1846,7 +1846,7 @@
         <v>79</v>
       </c>
       <c r="C36" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D36" t="s">
         <v>13</v>
@@ -1855,20 +1855,20 @@
         <v>80</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="I36" s="2"/>
       <c r="J36" s="2" t="s">
         <v>83</v>
       </c>
       <c r="K36" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
   </sheetData>
